--- a/AAII_Financials/Yearly/PFIS_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PFIS_YR_FIN.xlsx
@@ -1059,10 +1059,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10500</v>
+        <v>9800</v>
       </c>
       <c r="E15" s="3">
-        <v>8100</v>
+        <v>6800</v>
       </c>
       <c r="F15" s="3">
         <v>2900</v>
@@ -1302,10 +1302,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>83000</v>
+        <v>82300</v>
       </c>
       <c r="E21" s="3">
-        <v>32800</v>
+        <v>31400</v>
       </c>
       <c r="F21" s="3">
         <v>37200</v>
